--- a/backend/LPG testing/upload-CleanStep.xlsx
+++ b/backend/LPG testing/upload-CleanStep.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agarr\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/LPG testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2187DB-C16E-486E-8A9E-03C236752202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{8B2187DB-C16E-486E-8A9E-03C236752202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D07A24C6-F443-40C5-BBF5-85F3138D932D}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="21">
   <si>
     <t>Type - Inputs</t>
   </si>
@@ -108,7 +108,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,13 +154,6 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF002060"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -228,15 +221,15 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
+      <left style="thin">
+        <color auto="1"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
+      <top style="thin">
+        <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -245,7 +238,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -308,15 +301,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1379,8 +1382,8 @@
       <c r="B1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>3</v>
+      <c r="C1" s="6">
+        <v>2023</v>
       </c>
       <c r="D1" s="6">
         <v>2024</v>
@@ -1420,43 +1423,43 @@
       <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10">
-        <v>0</v>
-      </c>
-      <c r="D2" s="10">
-        <v>0</v>
-      </c>
-      <c r="E2" s="10">
-        <v>0</v>
-      </c>
-      <c r="F2" s="10">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0</v>
-      </c>
-      <c r="H2" s="10">
-        <v>0</v>
-      </c>
-      <c r="I2" s="10">
-        <v>0</v>
-      </c>
-      <c r="J2" s="10">
-        <v>0</v>
-      </c>
-      <c r="K2" s="10">
-        <v>0</v>
-      </c>
-      <c r="L2" s="10">
-        <v>0</v>
-      </c>
-      <c r="M2" s="10">
-        <v>0</v>
-      </c>
-      <c r="N2" s="10">
+      <c r="C2" s="24">
+        <v>0</v>
+      </c>
+      <c r="D2" s="24">
+        <v>0</v>
+      </c>
+      <c r="E2" s="24">
+        <v>0</v>
+      </c>
+      <c r="F2" s="24">
+        <v>0</v>
+      </c>
+      <c r="G2" s="24">
+        <v>0</v>
+      </c>
+      <c r="H2" s="24">
+        <v>0</v>
+      </c>
+      <c r="I2" s="24">
+        <v>0</v>
+      </c>
+      <c r="J2" s="24">
+        <v>0</v>
+      </c>
+      <c r="K2" s="24">
+        <v>0</v>
+      </c>
+      <c r="L2" s="24">
+        <v>0</v>
+      </c>
+      <c r="M2" s="24">
+        <v>0</v>
+      </c>
+      <c r="N2" s="24">
         <v>0</v>
       </c>
     </row>
@@ -1464,43 +1467,43 @@
       <c r="A3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="10">
-        <v>0</v>
-      </c>
-      <c r="D3" s="10">
-        <v>0</v>
-      </c>
-      <c r="E3" s="10">
-        <v>0</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0</v>
-      </c>
-      <c r="G3" s="10">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-      <c r="I3" s="10">
-        <v>0</v>
-      </c>
-      <c r="J3" s="10">
-        <v>0</v>
-      </c>
-      <c r="K3" s="10">
-        <v>0</v>
-      </c>
-      <c r="L3" s="10">
-        <v>0</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0</v>
-      </c>
-      <c r="N3" s="10">
+      <c r="C3" s="24">
+        <v>0</v>
+      </c>
+      <c r="D3" s="24">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24">
+        <v>0</v>
+      </c>
+      <c r="F3" s="24">
+        <v>0</v>
+      </c>
+      <c r="G3" s="24">
+        <v>0</v>
+      </c>
+      <c r="H3" s="24">
+        <v>0</v>
+      </c>
+      <c r="I3" s="24">
+        <v>0</v>
+      </c>
+      <c r="J3" s="24">
+        <v>0</v>
+      </c>
+      <c r="K3" s="24">
+        <v>0</v>
+      </c>
+      <c r="L3" s="24">
+        <v>0</v>
+      </c>
+      <c r="M3" s="24">
+        <v>0</v>
+      </c>
+      <c r="N3" s="24">
         <v>0</v>
       </c>
     </row>
@@ -1508,183 +1511,183 @@
       <c r="A4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="10">
-        <v>0</v>
-      </c>
-      <c r="D4" s="10">
-        <v>0</v>
-      </c>
-      <c r="E4" s="10">
-        <v>0</v>
-      </c>
-      <c r="F4" s="10">
-        <v>0</v>
-      </c>
-      <c r="G4" s="10">
-        <v>0</v>
-      </c>
-      <c r="H4" s="10">
-        <v>0</v>
-      </c>
-      <c r="I4" s="10">
-        <v>0</v>
-      </c>
-      <c r="J4" s="10">
-        <v>0</v>
-      </c>
-      <c r="K4" s="10">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10">
-        <v>0</v>
-      </c>
-      <c r="M4" s="10">
-        <v>0</v>
-      </c>
-      <c r="N4" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="24">
+        <v>0</v>
+      </c>
+      <c r="D4" s="24">
+        <v>0</v>
+      </c>
+      <c r="E4" s="24">
+        <v>0</v>
+      </c>
+      <c r="F4" s="24">
+        <v>0</v>
+      </c>
+      <c r="G4" s="24">
+        <v>0</v>
+      </c>
+      <c r="H4" s="24">
+        <v>0</v>
+      </c>
+      <c r="I4" s="24">
+        <v>0</v>
+      </c>
+      <c r="J4" s="24">
+        <v>0</v>
+      </c>
+      <c r="K4" s="24">
+        <v>0</v>
+      </c>
+      <c r="L4" s="24">
+        <v>0</v>
+      </c>
+      <c r="M4" s="24">
+        <v>0</v>
+      </c>
+      <c r="N4" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="N5" s="15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="26">
         <v>9.4411982377545986E-2</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="26">
         <v>0.17910918254928315</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="26">
         <v>0.17731809072379034</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="26">
         <v>0.17554490981655244</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="26">
         <v>0.17378946071838691</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="26">
         <v>0.17205156611120306</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="26">
         <v>0.13007825774755519</v>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="26">
         <v>8.8726452122599442E-2</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="26">
         <v>8.783918760137345E-2</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="26">
         <v>8.6960795725359696E-2</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="26">
         <v>8.609118776810612E-2</v>
       </c>
-      <c r="N6" s="23">
+      <c r="N6" s="26">
         <v>7.9676328396537641E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="10">
-        <v>0</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0</v>
-      </c>
-      <c r="G7" s="10">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10">
-        <v>0</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0</v>
-      </c>
-      <c r="J7" s="10">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0</v>
-      </c>
-      <c r="N7" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C7" s="24">
+        <v>0</v>
+      </c>
+      <c r="D7" s="24">
+        <v>0</v>
+      </c>
+      <c r="E7" s="24">
+        <v>0</v>
+      </c>
+      <c r="F7" s="24">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24">
+        <v>0</v>
+      </c>
+      <c r="H7" s="24">
+        <v>0</v>
+      </c>
+      <c r="I7" s="24">
+        <v>0</v>
+      </c>
+      <c r="J7" s="24">
+        <v>0</v>
+      </c>
+      <c r="K7" s="24">
+        <v>0</v>
+      </c>
+      <c r="L7" s="24">
+        <v>0</v>
+      </c>
+      <c r="M7" s="24">
+        <v>0</v>
+      </c>
+      <c r="N7" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="23" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="24">
@@ -1728,43 +1731,43 @@
       <c r="A9" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="27">
         <v>15</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="L9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="N9" s="19" t="s">
+      <c r="D9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="N9" s="27" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1785,8 +1788,8 @@
       <c r="B1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>3</v>
+      <c r="C1" s="6">
+        <v>2023</v>
       </c>
       <c r="D1" s="6">
         <v>2024</v>
